--- a/outputs/daily/hr_rankings_2026-06-29_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-29_full.xlsx
@@ -2786,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3068,28 +3064,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3906,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5318,34 +5314,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5602,34 +5594,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9506,34 +9494,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14242,34 +14226,30 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19542,34 +19522,30 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -21506,34 +21482,30 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23462,34 +23434,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -27922,34 +27890,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30434,34 +30398,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33230,34 +33190,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40470,34 +40426,30 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43258,34 +43210,30 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -45218,34 +45166,30 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46614,34 +46558,30 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54698,34 +54638,30 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -65828,34 +65764,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66110,28 +66042,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66948,34 +66884,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -68360,34 +68292,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -68644,34 +68572,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
